--- a/packages/db/research/season-trends/season-trends.xlsx
+++ b/packages/db/research/season-trends/season-trends.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="851">
   <si>
     <t>구분</t>
   </si>
@@ -90,6 +90,33 @@
     <t>성별</t>
   </si>
   <si>
+    <t>비온날평균</t>
+  </si>
+  <si>
+    <t>비온날수</t>
+  </si>
+  <si>
+    <t>안온날평균</t>
+  </si>
+  <si>
+    <t>안온날수</t>
+  </si>
+  <si>
+    <t>배</t>
+  </si>
+  <si>
+    <t>5℃ 미만</t>
+  </si>
+  <si>
+    <t>5~15℃</t>
+  </si>
+  <si>
+    <t>15~25℃</t>
+  </si>
+  <si>
+    <t>25℃ 이상</t>
+  </si>
+  <si>
     <t>술</t>
   </si>
   <si>
@@ -229,6 +256,12 @@
   </si>
   <si>
     <t>여</t>
+  </si>
+  <si>
+    <t>비</t>
+  </si>
+  <si>
+    <t>기온</t>
   </si>
   <si>
     <t>월</t>
@@ -2913,7 +2946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:AH87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="8" customWidth="1"/>
@@ -2921,9 +2954,12 @@
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="19" width="13" customWidth="1"/>
     <col min="20" max="25" width="8" customWidth="1"/>
+    <col min="27" max="27" width="8" customWidth="1"/>
+    <col min="29" max="30" width="8" customWidth="1"/>
+    <col min="33" max="34" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2999,16 +3035,43 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>100.2</v>
@@ -3068,18 +3131,18 @@
         <v>1.3</v>
       </c>
       <c r="W2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>136</v>
@@ -3139,18 +3202,18 @@
         <v>1.7</v>
       </c>
       <c r="W3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>124.6</v>
@@ -3210,18 +3273,18 @@
         <v>1.6</v>
       </c>
       <c r="W4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>113.2</v>
@@ -3281,18 +3344,18 @@
         <v>1.4</v>
       </c>
       <c r="W5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>117.7</v>
@@ -3352,18 +3415,18 @@
         <v>2.2</v>
       </c>
       <c r="W6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>129.9</v>
@@ -3423,18 +3486,18 @@
         <v>1.7</v>
       </c>
       <c r="W7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>132.7</v>
@@ -3494,18 +3557,18 @@
         <v>1.8</v>
       </c>
       <c r="W8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>99.5</v>
@@ -3565,18 +3628,18 @@
         <v>1.2</v>
       </c>
       <c r="W9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>85.6</v>
@@ -3636,18 +3699,18 @@
         <v>2.2</v>
       </c>
       <c r="W10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D11">
         <v>50.3</v>
@@ -3707,18 +3770,18 @@
         <v>4.8</v>
       </c>
       <c r="W11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D12">
         <v>117.7</v>
@@ -3778,18 +3841,18 @@
         <v>1.5</v>
       </c>
       <c r="W12" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>98.4</v>
@@ -3849,18 +3912,18 @@
         <v>1.2</v>
       </c>
       <c r="W13" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <v>153</v>
@@ -3920,18 +3983,18 @@
         <v>5.8</v>
       </c>
       <c r="W14" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D15">
         <v>100.9</v>
@@ -3991,18 +4054,18 @@
         <v>1.3</v>
       </c>
       <c r="W15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D16">
         <v>109.2</v>
@@ -4062,18 +4125,18 @@
         <v>1.7</v>
       </c>
       <c r="W16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D17">
         <v>27.9</v>
@@ -4133,18 +4196,18 @@
         <v>7</v>
       </c>
       <c r="W17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D18">
         <v>179.5</v>
@@ -4204,18 +4267,18 @@
         <v>17.1</v>
       </c>
       <c r="W18" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D19">
         <v>1.7</v>
@@ -4275,7 +4338,7 @@
         <v>234.5</v>
       </c>
       <c r="W19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -4283,7 +4346,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P20">
         <v>113.5</v>
@@ -4304,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="X20" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -4312,7 +4375,7 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P21">
         <v>109.5</v>
@@ -4333,7 +4396,7 @@
         <v>10</v>
       </c>
       <c r="X21" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -4341,7 +4404,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P22">
         <v>108.6</v>
@@ -4362,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="X22" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -4370,7 +4433,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P23">
         <v>111.2</v>
@@ -4391,7 +4454,7 @@
         <v>10</v>
       </c>
       <c r="X23" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -4399,7 +4462,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P24">
         <v>88</v>
@@ -4420,7 +4483,7 @@
         <v>8</v>
       </c>
       <c r="X24" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -4428,7 +4491,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P25">
         <v>85.2</v>
@@ -4449,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="X25" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -4457,7 +4520,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P26">
         <v>80.9</v>
@@ -4478,7 +4541,7 @@
         <v>9</v>
       </c>
       <c r="X26" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -4486,7 +4549,7 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P27">
         <v>81.4</v>
@@ -4507,7 +4570,7 @@
         <v>9</v>
       </c>
       <c r="X27" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -4515,7 +4578,7 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P28">
         <v>90.2</v>
@@ -4536,7 +4599,7 @@
         <v>8</v>
       </c>
       <c r="X28" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -4544,7 +4607,7 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P29">
         <v>90.3</v>
@@ -4565,7 +4628,7 @@
         <v>8</v>
       </c>
       <c r="X29" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -4573,7 +4636,7 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P30">
         <v>91.3</v>
@@ -4594,7 +4657,7 @@
         <v>8</v>
       </c>
       <c r="X30" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -4602,7 +4665,7 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P31">
         <v>92.7</v>
@@ -4623,7 +4686,7 @@
         <v>9</v>
       </c>
       <c r="X31" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -4631,7 +4694,7 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P32">
         <v>88.7</v>
@@ -4652,7 +4715,7 @@
         <v>6</v>
       </c>
       <c r="X32" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -4660,7 +4723,7 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P33">
         <v>87.2</v>
@@ -4681,7 +4744,7 @@
         <v>6</v>
       </c>
       <c r="X33" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -4689,7 +4752,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P34">
         <v>89.2</v>
@@ -4710,7 +4773,7 @@
         <v>6</v>
       </c>
       <c r="X34" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -4718,7 +4781,7 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P35">
         <v>89.4</v>
@@ -4739,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="X35" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -4747,7 +4810,7 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P36">
         <v>85.6</v>
@@ -4768,7 +4831,7 @@
         <v>8</v>
       </c>
       <c r="X36" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -4776,7 +4839,7 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P37">
         <v>88.3</v>
@@ -4797,7 +4860,7 @@
         <v>8</v>
       </c>
       <c r="X37" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -4805,7 +4868,7 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P38">
         <v>89</v>
@@ -4826,7 +4889,7 @@
         <v>9</v>
       </c>
       <c r="X38" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
@@ -4834,7 +4897,7 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P39">
         <v>90.6</v>
@@ -4855,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="X39" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
@@ -4863,7 +4926,7 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P40">
         <v>93</v>
@@ -4884,7 +4947,7 @@
         <v>11</v>
       </c>
       <c r="X40" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
@@ -4892,7 +4955,7 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P41">
         <v>94.1</v>
@@ -4913,7 +4976,7 @@
         <v>11</v>
       </c>
       <c r="X41" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
@@ -4921,7 +4984,7 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P42">
         <v>92.3</v>
@@ -4942,7 +5005,7 @@
         <v>11</v>
       </c>
       <c r="X42" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -4950,7 +5013,7 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P43">
         <v>89.5</v>
@@ -4971,7 +5034,7 @@
         <v>11</v>
       </c>
       <c r="X43" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -4979,7 +5042,7 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P44">
         <v>89.8</v>
@@ -5000,7 +5063,7 @@
         <v>11</v>
       </c>
       <c r="X44" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
@@ -5008,7 +5071,7 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P45">
         <v>94.9</v>
@@ -5029,7 +5092,7 @@
         <v>9</v>
       </c>
       <c r="X45" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
@@ -5037,7 +5100,7 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P46">
         <v>94.4</v>
@@ -5058,7 +5121,7 @@
         <v>9</v>
       </c>
       <c r="X46" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -5066,7 +5129,7 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P47">
         <v>95.3</v>
@@ -5087,7 +5150,7 @@
         <v>9</v>
       </c>
       <c r="X47" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
@@ -5095,7 +5158,7 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P48">
         <v>99.4</v>
@@ -5116,7 +5179,7 @@
         <v>11</v>
       </c>
       <c r="X48" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
@@ -5124,7 +5187,7 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P49">
         <v>99.4</v>
@@ -5145,7 +5208,7 @@
         <v>4</v>
       </c>
       <c r="X49" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
@@ -5153,7 +5216,7 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P50">
         <v>99.3</v>
@@ -5174,7 +5237,7 @@
         <v>4</v>
       </c>
       <c r="X50" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
@@ -5182,7 +5245,7 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P51">
         <v>99.5</v>
@@ -5203,7 +5266,7 @@
         <v>4</v>
       </c>
       <c r="X51" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
@@ -5211,7 +5274,7 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P52">
         <v>111</v>
@@ -5232,7 +5295,7 @@
         <v>10</v>
       </c>
       <c r="Y52" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
@@ -5240,7 +5303,7 @@
         <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P53">
         <v>109.8</v>
@@ -5261,7 +5324,7 @@
         <v>10</v>
       </c>
       <c r="Y53" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
@@ -5269,7 +5332,7 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P54">
         <v>85.6</v>
@@ -5290,7 +5353,7 @@
         <v>9</v>
       </c>
       <c r="Y54" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
@@ -5298,7 +5361,7 @@
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P55">
         <v>83.2</v>
@@ -5319,7 +5382,7 @@
         <v>9</v>
       </c>
       <c r="Y55" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
@@ -5327,7 +5390,7 @@
         <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P56">
         <v>92.4</v>
@@ -5348,7 +5411,7 @@
         <v>8</v>
       </c>
       <c r="Y56" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
@@ -5356,7 +5419,7 @@
         <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P57">
         <v>88.8</v>
@@ -5377,7 +5440,7 @@
         <v>8</v>
       </c>
       <c r="Y57" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
@@ -5385,7 +5448,7 @@
         <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P58">
         <v>90</v>
@@ -5406,7 +5469,7 @@
         <v>6</v>
       </c>
       <c r="Y58" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
@@ -5414,7 +5477,7 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P59">
         <v>86.8</v>
@@ -5435,7 +5498,7 @@
         <v>6</v>
       </c>
       <c r="Y59" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
@@ -5443,7 +5506,7 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P60">
         <v>90.7</v>
@@ -5464,7 +5527,7 @@
         <v>8</v>
       </c>
       <c r="Y60" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
@@ -5472,7 +5535,7 @@
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P61">
         <v>86.3</v>
@@ -5493,7 +5556,7 @@
         <v>8</v>
       </c>
       <c r="Y61" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
@@ -5501,7 +5564,7 @@
         <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P62">
         <v>92.4</v>
@@ -5522,7 +5585,7 @@
         <v>11</v>
       </c>
       <c r="Y62" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -5530,7 +5593,7 @@
         <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P63">
         <v>90.1</v>
@@ -5551,7 +5614,7 @@
         <v>11</v>
       </c>
       <c r="Y63" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
@@ -5559,7 +5622,7 @@
         <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P64">
         <v>94.1</v>
@@ -5580,7 +5643,7 @@
         <v>11</v>
       </c>
       <c r="Y64" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
@@ -5588,7 +5651,7 @@
         <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P65">
         <v>90.8</v>
@@ -5609,7 +5672,7 @@
         <v>11</v>
       </c>
       <c r="Y65" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
@@ -5617,7 +5680,7 @@
         <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P66">
         <v>99</v>
@@ -5638,7 +5701,7 @@
         <v>4</v>
       </c>
       <c r="Y66" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
@@ -5646,7 +5709,7 @@
         <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P67">
         <v>98.2</v>
@@ -5667,7 +5730,437 @@
         <v>4</v>
       </c>
       <c r="Y67" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z68">
+        <v>12.5</v>
+      </c>
+      <c r="AA68">
+        <v>150</v>
+      </c>
+      <c r="AB68">
+        <v>10.5</v>
+      </c>
+      <c r="AC68">
+        <v>580</v>
+      </c>
+      <c r="AD68">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z69">
+        <v>1.9</v>
+      </c>
+      <c r="AA69">
+        <v>150</v>
+      </c>
+      <c r="AB69">
+        <v>2.1</v>
+      </c>
+      <c r="AC69">
+        <v>580</v>
+      </c>
+      <c r="AD69">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z70">
+        <v>16.9</v>
+      </c>
+      <c r="AA70">
+        <v>150</v>
+      </c>
+      <c r="AB70">
+        <v>17.2</v>
+      </c>
+      <c r="AC70">
+        <v>580</v>
+      </c>
+      <c r="AD70">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71">
+        <v>13.8</v>
+      </c>
+      <c r="AA71">
+        <v>150</v>
+      </c>
+      <c r="AB71">
+        <v>15.1</v>
+      </c>
+      <c r="AC71">
+        <v>580</v>
+      </c>
+      <c r="AD71">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z72">
+        <v>32.8</v>
+      </c>
+      <c r="AA72">
+        <v>150</v>
+      </c>
+      <c r="AB72">
+        <v>18.9</v>
+      </c>
+      <c r="AC72">
+        <v>580</v>
+      </c>
+      <c r="AD72">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z73">
+        <v>21.4</v>
+      </c>
+      <c r="AA73">
+        <v>150</v>
+      </c>
+      <c r="AB73">
+        <v>23</v>
+      </c>
+      <c r="AC73">
+        <v>580</v>
+      </c>
+      <c r="AD73">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z74">
+        <v>40.7</v>
+      </c>
+      <c r="AA74">
+        <v>150</v>
+      </c>
+      <c r="AB74">
+        <v>40.8</v>
+      </c>
+      <c r="AC74">
+        <v>580</v>
+      </c>
+      <c r="AD74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z75">
+        <v>0.2</v>
+      </c>
+      <c r="AA75">
+        <v>126</v>
+      </c>
+      <c r="AB75">
+        <v>0.1</v>
+      </c>
+      <c r="AC75">
+        <v>122</v>
+      </c>
+      <c r="AD75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" t="s">
         <v>71</v>
+      </c>
+      <c r="Z76">
+        <v>1.9</v>
+      </c>
+      <c r="AA76">
+        <v>150</v>
+      </c>
+      <c r="AB76">
+        <v>2.8</v>
+      </c>
+      <c r="AC76">
+        <v>580</v>
+      </c>
+      <c r="AD76">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>64</v>
+      </c>
+      <c r="AB77">
+        <v>0.1</v>
+      </c>
+      <c r="AC77">
+        <v>194</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE78">
+        <v>11.5</v>
+      </c>
+      <c r="AF78">
+        <v>11</v>
+      </c>
+      <c r="AG78">
+        <v>11.5</v>
+      </c>
+      <c r="AH78">
+        <v>9.2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE79">
+        <v>2.6</v>
+      </c>
+      <c r="AF79">
+        <v>2</v>
+      </c>
+      <c r="AG79">
+        <v>1.9</v>
+      </c>
+      <c r="AH79">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE80">
+        <v>20.6</v>
+      </c>
+      <c r="AF80">
+        <v>16.4</v>
+      </c>
+      <c r="AG80">
+        <v>16.7</v>
+      </c>
+      <c r="AH80">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE81">
+        <v>19.3</v>
+      </c>
+      <c r="AF81">
+        <v>14.7</v>
+      </c>
+      <c r="AG81">
+        <v>13.3</v>
+      </c>
+      <c r="AH81">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE82">
+        <v>18.3</v>
+      </c>
+      <c r="AF82">
+        <v>19.7</v>
+      </c>
+      <c r="AG82">
+        <v>24.4</v>
+      </c>
+      <c r="AH82">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE83">
+        <v>11.2</v>
+      </c>
+      <c r="AF83">
+        <v>15.6</v>
+      </c>
+      <c r="AG83">
+        <v>25</v>
+      </c>
+      <c r="AH83">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE84">
+        <v>46.9</v>
+      </c>
+      <c r="AF84">
+        <v>42.8</v>
+      </c>
+      <c r="AG84">
+        <v>38.3</v>
+      </c>
+      <c r="AH84">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE85">
+        <v>0.1</v>
+      </c>
+      <c r="AF85">
+        <v>0.1</v>
+      </c>
+      <c r="AG85">
+        <v>0.2</v>
+      </c>
+      <c r="AH85">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE86">
+        <v>5.7</v>
+      </c>
+      <c r="AF86">
+        <v>2.9</v>
+      </c>
+      <c r="AG86">
+        <v>1.1</v>
+      </c>
+      <c r="AH86">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>0</v>
+      </c>
+      <c r="AG87">
+        <v>0</v>
+      </c>
+      <c r="AH87">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -5687,66 +6180,66 @@
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>34.80728</v>
@@ -5805,7 +6298,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>34.3313</v>
@@ -5864,7 +6357,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B4">
         <v>37.08692</v>
@@ -5923,7 +6416,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B5">
         <v>34.98183</v>
@@ -5982,7 +6475,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B6">
         <v>39.38759</v>
@@ -6041,7 +6534,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <v>44.80103</v>
@@ -6100,7 +6593,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B8">
         <v>44.90749</v>
@@ -6159,7 +6652,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B9">
         <v>44.41789</v>
@@ -6218,7 +6711,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B10">
         <v>42.01942</v>
@@ -6277,7 +6770,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B11">
         <v>44.356</v>
@@ -6336,7 +6829,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B12">
         <v>33.77176</v>
@@ -6395,7 +6888,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B13">
         <v>38.11377</v>
@@ -6454,7 +6947,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B14">
         <v>37.71516</v>
@@ -6513,7 +7006,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B15">
         <v>35.98207</v>
@@ -6572,7 +7065,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B16">
         <v>32.87179</v>
@@ -6631,7 +7124,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B17">
         <v>38.63741</v>
@@ -6690,7 +7183,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B18">
         <v>34.41981</v>
@@ -6749,7 +7242,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B19">
         <v>37.19709</v>
@@ -6808,7 +7301,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B20">
         <v>34.47552</v>
@@ -6867,7 +7360,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B21">
         <v>42.3778</v>
@@ -6926,7 +7419,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B22">
         <v>34.6643</v>
@@ -6985,7 +7478,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B23">
         <v>29.62596</v>
@@ -7044,7 +7537,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B24">
         <v>28.52916</v>
@@ -7103,7 +7596,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B25">
         <v>29.64886</v>
@@ -7162,7 +7655,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B26">
         <v>28.21287</v>
@@ -7221,7 +7714,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B27">
         <v>23.39302</v>
@@ -7280,7 +7773,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B28">
         <v>23.52547</v>
@@ -7339,7 +7832,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B29">
         <v>23.03092</v>
@@ -7398,7 +7891,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B30">
         <v>21.65435</v>
@@ -7457,7 +7950,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B31">
         <v>22.81305</v>
@@ -7516,7 +8009,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B32">
         <v>23.32988</v>
@@ -7575,7 +8068,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B33">
         <v>23.27232</v>
@@ -7631,7 +8124,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B34">
         <v>18.45432</v>
@@ -7687,7 +8180,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B35">
         <v>20.05558</v>
@@ -7743,7 +8236,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B36">
         <v>20.93574</v>
@@ -7799,7 +8292,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B37">
         <v>19.59198</v>
@@ -7866,42 +8359,42 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>12.95721</v>
@@ -7936,7 +8429,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>12.53877</v>
@@ -7971,7 +8464,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <v>13.49109</v>
@@ -8006,7 +8499,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>12.75521</v>
@@ -8041,7 +8534,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>14.60212</v>
@@ -8076,7 +8569,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B7">
         <v>15.71315</v>
@@ -8111,7 +8604,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B8">
         <v>13.10872</v>
@@ -8146,7 +8639,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B9">
         <v>13.45501</v>
@@ -8181,7 +8674,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B10">
         <v>12.81292</v>
@@ -8216,7 +8709,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B11">
         <v>12.36563</v>
@@ -8251,7 +8744,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B12">
         <v>13.12315</v>
@@ -8286,7 +8779,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B13">
         <v>13.43337</v>
@@ -8321,7 +8814,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B14">
         <v>13.06543</v>
@@ -8356,7 +8849,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B15">
         <v>17.43741</v>
@@ -8391,7 +8884,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B16">
         <v>14.86905</v>
@@ -8426,7 +8919,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B17">
         <v>13.20972</v>
@@ -8461,7 +8954,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B18">
         <v>13.71473</v>
@@ -8496,7 +8989,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B19">
         <v>23.87995</v>
@@ -8531,7 +9024,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B20">
         <v>14.33518</v>
@@ -8566,7 +9059,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B21">
         <v>11.4566</v>
@@ -8601,7 +9094,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B22">
         <v>12.52434</v>
@@ -8636,7 +9129,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B23">
         <v>21.83825</v>
@@ -8671,7 +9164,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B24">
         <v>13.67145</v>
@@ -8706,7 +9199,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B25">
         <v>12.44498</v>
@@ -8741,7 +9234,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B26">
         <v>13.45501</v>
@@ -8776,7 +9269,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B27">
         <v>14.1981</v>
@@ -8811,7 +9304,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B28">
         <v>13.98167</v>
@@ -8846,7 +9339,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B29">
         <v>13.55602</v>
@@ -8881,7 +9374,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B30">
         <v>13.20251</v>
@@ -8916,7 +9409,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B31">
         <v>13.76524</v>
@@ -8951,7 +9444,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B32">
         <v>14.63819</v>
@@ -8986,7 +9479,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B33">
         <v>18.93081</v>
@@ -9021,7 +9514,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B34">
         <v>16.61496</v>
@@ -9056,7 +9549,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B35">
         <v>13.15922</v>
@@ -9091,7 +9584,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B36">
         <v>12.95721</v>
@@ -9126,7 +9619,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B37">
         <v>13.06543</v>
@@ -9161,7 +9654,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B38">
         <v>13.62095</v>
@@ -9196,7 +9689,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B39">
         <v>13.10872</v>
@@ -9231,7 +9724,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B40">
         <v>13.49109</v>
@@ -9266,7 +9759,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B41">
         <v>13.65702</v>
@@ -9301,7 +9794,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B42">
         <v>12.85621</v>
@@ -9336,7 +9829,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B43">
         <v>12.84178</v>
@@ -9371,7 +9864,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B44">
         <v>12.43777</v>
@@ -9406,7 +9899,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B45">
         <v>12.83457</v>
@@ -9441,7 +9934,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B46">
         <v>13.98888</v>
@@ -9476,7 +9969,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B47">
         <v>13.65702</v>
@@ -9511,7 +10004,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B48">
         <v>16.84582</v>
@@ -9546,7 +10039,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B49">
         <v>18.95245</v>
@@ -9581,7 +10074,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B50">
         <v>13.4478</v>
@@ -9616,7 +10109,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B51">
         <v>13.96724</v>
@@ -9651,7 +10144,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B52">
         <v>12.8995</v>
@@ -9686,7 +10179,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B53">
         <v>13.38287</v>
@@ -9721,7 +10214,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B54">
         <v>13.88788</v>
@@ -9756,7 +10249,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B55">
         <v>13.32515</v>
@@ -9791,7 +10284,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B56">
         <v>12.32955</v>
@@ -9826,7 +10319,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B57">
         <v>12.51713</v>
@@ -9861,7 +10354,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B58">
         <v>15.54</v>
@@ -9896,7 +10389,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B59">
         <v>14.50833</v>
@@ -9931,7 +10424,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B60">
         <v>13.59209</v>
@@ -9966,7 +10459,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B61">
         <v>13.46223</v>
@@ -10001,7 +10494,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B62">
         <v>13.51994</v>
@@ -10036,7 +10529,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B63">
         <v>12.19969</v>
@@ -10071,7 +10564,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B64">
         <v>11.54317</v>
@@ -10106,7 +10599,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B65">
         <v>11.97604</v>
@@ -10141,7 +10634,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B66">
         <v>9.94877</v>
@@ -10176,7 +10669,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B67">
         <v>12.12033</v>
@@ -10211,7 +10704,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B68">
         <v>11.31952</v>
@@ -10246,7 +10739,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B69">
         <v>11.93276</v>
@@ -10281,7 +10774,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B70">
         <v>12.69028</v>
@@ -10316,7 +10809,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B71">
         <v>11.66582</v>
@@ -10351,7 +10844,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B72">
         <v>11.64418</v>
@@ -10386,7 +10879,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B73">
         <v>13.3973</v>
@@ -10421,7 +10914,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B74">
         <v>12.01933</v>
@@ -10456,7 +10949,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B75">
         <v>12.48106</v>
@@ -10491,7 +10984,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B76">
         <v>12.73356</v>
@@ -10526,7 +11019,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B77">
         <v>13.31794</v>
@@ -10561,7 +11054,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B78">
         <v>12.40891</v>
@@ -10596,7 +11089,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B79">
         <v>12.32955</v>
@@ -10631,7 +11124,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B80">
         <v>13.80852</v>
@@ -10666,7 +11159,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B81">
         <v>13.57044</v>
@@ -10701,7 +11194,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B82">
         <v>13.42615</v>
@@ -10736,7 +11229,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B83">
         <v>12.97886</v>
@@ -10771,7 +11264,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B84">
         <v>15.18649</v>
@@ -10806,7 +11299,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B85">
         <v>12.19969</v>
@@ -10841,7 +11334,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B86">
         <v>11.89668</v>
@@ -10876,7 +11369,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B87">
         <v>13.63537</v>
@@ -10911,7 +11404,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B88">
         <v>11.39167</v>
@@ -10946,7 +11439,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B89">
         <v>14.40732</v>
@@ -10981,7 +11474,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B90">
         <v>12.4522</v>
@@ -11016,7 +11509,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B91">
         <v>10.60529</v>
@@ -11051,7 +11544,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B92">
         <v>10.37443</v>
@@ -11086,7 +11579,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B93">
         <v>11.48546</v>
@@ -11121,7 +11614,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B94">
         <v>12.74078</v>
@@ -11156,7 +11649,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B95">
         <v>11.58646</v>
@@ -11191,7 +11684,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B96">
         <v>11.39167</v>
@@ -11226,7 +11719,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B97">
         <v>12.85621</v>
@@ -11261,7 +11754,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B98">
         <v>13.76524</v>
@@ -11296,7 +11789,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B99">
         <v>12.56763</v>
@@ -11331,7 +11824,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B100">
         <v>12.1059</v>
@@ -11366,7 +11859,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B101">
         <v>12.27905</v>
@@ -11401,7 +11894,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B102">
         <v>23.28114</v>
@@ -11436,7 +11929,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B103">
         <v>22.79777</v>
@@ -11471,7 +11964,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B104">
         <v>19.34925</v>
@@ -11506,7 +11999,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B105">
         <v>15.84301</v>
@@ -11541,7 +12034,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B106">
         <v>14.25582</v>
@@ -11576,7 +12069,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B107">
         <v>14.93398</v>
@@ -11611,7 +12104,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B108">
         <v>13.03657</v>
@@ -11646,7 +12139,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B109">
         <v>13.30351</v>
@@ -11681,7 +12174,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B110">
         <v>13.90231</v>
@@ -11716,7 +12209,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B111">
         <v>13.98167</v>
@@ -11751,7 +12244,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B112">
         <v>13.11593</v>
@@ -11786,7 +12279,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B113">
         <v>14.34961</v>
@@ -11821,7 +12314,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B114">
         <v>13.9961</v>
@@ -11856,7 +12349,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B115">
         <v>14.4434</v>
@@ -11891,7 +12384,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B116">
         <v>14.56604</v>
@@ -11926,7 +12419,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B117">
         <v>12.51713</v>
@@ -11961,7 +12454,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B118">
         <v>12.40891</v>
@@ -11996,7 +12489,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B119">
         <v>13.48387</v>
@@ -12031,7 +12524,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B120">
         <v>13.81574</v>
@@ -12066,7 +12559,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B121">
         <v>19.06788</v>
@@ -12101,7 +12594,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B122">
         <v>17.50955</v>
@@ -12136,7 +12629,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B123">
         <v>14.37847</v>
@@ -12171,7 +12664,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B124">
         <v>12.71914</v>
@@ -12206,7 +12699,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B125">
         <v>16.26145</v>
@@ -12241,7 +12734,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B126">
         <v>13.61373</v>
@@ -12276,7 +12769,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B127">
         <v>11.21131</v>
@@ -12311,7 +12804,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B128">
         <v>11.86061</v>
@@ -12346,7 +12839,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B129">
         <v>12.43777</v>
@@ -12381,7 +12874,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B130">
         <v>12.24298</v>
@@ -12416,7 +12909,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B131">
         <v>12.31512</v>
@@ -12451,7 +12944,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B132">
         <v>16.26866</v>
@@ -12486,7 +12979,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B133">
         <v>15.12877</v>
@@ -12521,7 +13014,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B134">
         <v>12.52434</v>
@@ -12556,7 +13049,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B135">
         <v>13.39008</v>
@@ -12591,7 +13084,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B136">
         <v>14.68148</v>
@@ -12626,7 +13119,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B137">
         <v>12.71192</v>
@@ -12661,7 +13154,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B138">
         <v>12.84178</v>
@@ -12696,7 +13189,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B139">
         <v>26.28237</v>
@@ -12731,7 +13224,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B140">
         <v>24.04588</v>
@@ -12766,7 +13259,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B141">
         <v>14.1981</v>
@@ -12801,7 +13294,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B142">
         <v>13.20972</v>
@@ -12836,7 +13329,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B143">
         <v>12.99329</v>
@@ -12871,7 +13364,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B144">
         <v>13.1015</v>
@@ -12906,7 +13399,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B145">
         <v>13.49109</v>
@@ -12941,7 +13434,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B146">
         <v>15.35964</v>
@@ -12976,7 +13469,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B147">
         <v>14.98448</v>
@@ -13011,7 +13504,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B148">
         <v>12.94278</v>
@@ -13046,7 +13539,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B149">
         <v>14.36404</v>
@@ -13081,7 +13574,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B150">
         <v>13.11593</v>
@@ -13116,7 +13609,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B151">
         <v>12.6037</v>
@@ -13151,7 +13644,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B152">
         <v>13.00771</v>
@@ -13186,7 +13679,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B153">
         <v>18.26708</v>
@@ -13221,7 +13714,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B154">
         <v>23.22343</v>
@@ -13256,7 +13749,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B155">
         <v>16.23259</v>
@@ -13291,7 +13784,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B156">
         <v>13.51994</v>
@@ -13326,7 +13819,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B157">
         <v>11.53596</v>
@@ -13361,7 +13854,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B158">
         <v>12.41613</v>
@@ -13396,7 +13889,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B159">
         <v>12.48827</v>
@@ -13431,7 +13924,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B160">
         <v>14.78248</v>
@@ -13466,7 +13959,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B161">
         <v>13.67866</v>
@@ -13501,7 +13994,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B162">
         <v>12.70471</v>
@@ -13536,7 +14029,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B163">
         <v>12.57485</v>
@@ -13571,7 +14064,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B164">
         <v>13.05822</v>
@@ -13606,7 +14099,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B165">
         <v>12.04097</v>
@@ -13641,7 +14134,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B166">
         <v>12.28627</v>
@@ -13676,7 +14169,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B167">
         <v>16.45624</v>
@@ -13711,7 +14204,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B168">
         <v>16.83139</v>
@@ -13746,7 +14239,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B169">
         <v>12.3512</v>
@@ -13781,7 +14274,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B170">
         <v>14.98448</v>
@@ -13816,7 +14309,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B171">
         <v>13.33237</v>
@@ -13851,7 +14344,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B172">
         <v>13.28186</v>
@@ -13886,7 +14379,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B173">
         <v>15.07106</v>
@@ -13921,7 +14414,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B174">
         <v>15.3885</v>
@@ -13956,7 +14449,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B175">
         <v>14.58047</v>
@@ -13991,7 +14484,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="B176">
         <v>12.30791</v>
@@ -14026,7 +14519,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B177">
         <v>12.46663</v>
@@ -14061,7 +14554,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B178">
         <v>12.32955</v>
@@ -14096,7 +14589,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B179">
         <v>14.01053</v>
@@ -14131,7 +14624,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B180">
         <v>13.73638</v>
@@ -14166,7 +14659,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B181">
         <v>13.68588</v>
@@ -14201,7 +14694,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B182">
         <v>12.97886</v>
@@ -14236,7 +14729,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B183">
         <v>10.9588</v>
@@ -14271,7 +14764,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B184">
         <v>11.44217</v>
@@ -14306,7 +14799,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B185">
         <v>13.04379</v>
@@ -14341,7 +14834,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B186">
         <v>11.65861</v>
@@ -14376,7 +14869,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B187">
         <v>12.16362</v>
@@ -14411,7 +14904,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="B188">
         <v>20.97251</v>
@@ -14446,7 +14939,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B189">
         <v>12.75521</v>
@@ -14481,7 +14974,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B190">
         <v>11.55039</v>
@@ -14516,7 +15009,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B191">
         <v>12.56763</v>
@@ -14551,7 +15044,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B192">
         <v>13.97446</v>
@@ -14586,7 +15079,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B193">
         <v>12.19248</v>
@@ -14621,7 +15114,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="B194">
         <v>13.07264</v>
@@ -14656,7 +15149,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B195">
         <v>21.55688</v>
@@ -14691,7 +15184,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B196">
         <v>13.41894</v>
@@ -14726,7 +15219,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B197">
         <v>17.40134</v>
@@ -14761,7 +15254,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B198">
         <v>11.73075</v>
@@ -14796,7 +15289,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B199">
         <v>11.11752</v>
@@ -14831,7 +15324,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B200">
         <v>11.51432</v>
@@ -14866,7 +15359,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B201">
         <v>12.69749</v>
@@ -14901,7 +15394,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B202">
         <v>17.80535</v>
@@ -14936,7 +15429,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B203">
         <v>13.75802</v>
@@ -14971,7 +15464,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B204">
         <v>10.84337</v>
@@ -15006,7 +15499,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B205">
         <v>24.12524</v>
@@ -15041,7 +15534,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B206">
         <v>11.69468</v>
@@ -15076,7 +15569,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B207">
         <v>11.22574</v>
@@ -15111,7 +15604,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B208">
         <v>11.06702</v>
@@ -15146,7 +15639,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B209">
         <v>11.57203</v>
@@ -15181,7 +15674,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B210">
         <v>12.14198</v>
@@ -15216,7 +15709,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B211">
         <v>10.83615</v>
@@ -15251,7 +15744,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B212">
         <v>10.93716</v>
@@ -15286,7 +15779,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B213">
         <v>11.00209</v>
@@ -15321,7 +15814,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B214">
         <v>19.74605</v>
@@ -15356,7 +15849,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B215">
         <v>11.55039</v>
@@ -15391,7 +15884,7 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B216">
         <v>15.29471</v>
@@ -15426,7 +15919,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B217">
         <v>12.56763</v>
@@ -15461,7 +15954,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B218">
         <v>13.65702</v>
@@ -15496,7 +15989,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B219">
         <v>12.23576</v>
@@ -15531,7 +16024,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B220">
         <v>10.46822</v>
@@ -15566,7 +16059,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B221">
         <v>11.54317</v>
@@ -15601,7 +16094,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B222">
         <v>24.16853</v>
@@ -15636,7 +16129,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B223">
         <v>16.6871</v>
@@ -15671,7 +16164,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B224">
         <v>13.72916</v>
@@ -15706,7 +16199,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B225">
         <v>12.48827</v>
@@ -15741,7 +16234,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B226">
         <v>12.82014</v>
@@ -15776,7 +16269,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B227">
         <v>12.71914</v>
@@ -15811,7 +16304,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B228">
         <v>14.70312</v>
@@ -15846,7 +16339,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B229">
         <v>25.51042</v>
@@ -15881,7 +16374,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B230">
         <v>16.17487</v>
@@ -15916,7 +16409,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B231">
         <v>20.30878</v>
@@ -15951,7 +16444,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B232">
         <v>13.59209</v>
@@ -15986,7 +16479,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B233">
         <v>12.84178</v>
@@ -16021,7 +16514,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B234">
         <v>12.17083</v>
@@ -16056,7 +16549,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B235">
         <v>13.03657</v>
@@ -16091,7 +16584,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B236">
         <v>14.06824</v>
@@ -16126,7 +16619,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B237">
         <v>18.82259</v>
@@ -16161,7 +16654,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B238">
         <v>21.10958</v>
@@ -16196,7 +16689,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B239">
         <v>21.50638</v>
@@ -16231,7 +16724,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B240">
         <v>21.16008</v>
@@ -16266,7 +16759,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B241">
         <v>18.79373</v>
@@ -16301,7 +16794,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B242">
         <v>17.59613</v>
@@ -16336,7 +16829,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B243">
         <v>16.19652</v>
@@ -16371,7 +16864,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B244">
         <v>16.67989</v>
@@ -16406,7 +16899,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B245">
         <v>15.46785</v>
@@ -16441,7 +16934,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B246">
         <v>18.08671</v>
@@ -16476,7 +16969,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B247">
         <v>15.54721</v>
@@ -16511,7 +17004,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B248">
         <v>12.44498</v>
@@ -16546,7 +17039,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B249">
         <v>13.37565</v>
@@ -16581,7 +17074,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B250">
         <v>14.11875</v>
@@ -16613,7 +17106,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B251">
         <v>14.02496</v>
@@ -16645,7 +17138,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B252">
         <v>11.98326</v>
@@ -16677,7 +17170,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B253">
         <v>10.8073</v>
@@ -16709,7 +17202,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B254">
         <v>11.29788</v>
@@ -16741,7 +17234,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B255">
         <v>11.29788</v>
@@ -16773,7 +17266,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B256">
         <v>13.0005</v>
@@ -16805,7 +17298,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B257">
         <v>18.70716</v>
@@ -16837,7 +17330,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B258">
         <v>14.88348</v>
@@ -16869,7 +17362,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B259">
         <v>13.07264</v>
@@ -16901,7 +17394,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B260">
         <v>12.95721</v>
@@ -16930,7 +17423,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B261">
         <v>11.5071</v>
@@ -16959,7 +17452,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B262">
         <v>12.08426</v>
@@ -16988,7 +17481,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B263">
         <v>12.34398</v>
@@ -17017,7 +17510,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B264">
         <v>23.49036</v>
@@ -17046,7 +17539,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B265">
         <v>17.40855</v>
@@ -17075,7 +17568,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B266">
         <v>11.68746</v>
@@ -17104,7 +17597,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B267">
         <v>9.94877</v>
@@ -17133,7 +17626,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B268">
         <v>15.86465</v>
@@ -17162,7 +17655,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B269">
         <v>16.25423</v>
@@ -17191,7 +17684,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B270">
         <v>11.06702</v>
@@ -17220,7 +17713,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B271">
         <v>10.55479</v>
@@ -17249,7 +17742,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B272">
         <v>11.61532</v>
@@ -17278,7 +17771,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B273">
         <v>9.8117</v>
@@ -17307,7 +17800,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B274">
         <v>9.32833</v>
@@ -17336,7 +17829,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B275">
         <v>9.0181</v>
@@ -17365,7 +17858,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B276">
         <v>10.04977</v>
@@ -17394,7 +17887,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B277">
         <v>9.5664</v>
@@ -17423,7 +17916,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B278">
         <v>10.19406</v>
@@ -17452,7 +17945,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B279">
         <v>10.16521</v>
@@ -17481,7 +17974,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B280">
         <v>9.5664</v>
@@ -17510,7 +18003,7 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B281">
         <v>8.83774</v>
@@ -17539,7 +18032,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B282">
         <v>10.30228</v>
@@ -17568,7 +18061,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B283">
         <v>10.04256</v>
@@ -17597,7 +18090,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B284">
         <v>10.23014</v>
@@ -17626,7 +18119,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B285">
         <v>10.69908</v>
@@ -17655,7 +18148,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B286">
         <v>11.23295</v>
@@ -17684,7 +18177,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B287">
         <v>12.74799</v>
@@ -17713,7 +18206,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B288">
         <v>14.78969</v>
@@ -17742,7 +18235,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B289">
         <v>12.6542</v>
@@ -17771,7 +18264,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B290">
         <v>20.17891</v>
@@ -17800,7 +18293,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B291">
         <v>18.89474</v>
@@ -17829,7 +18322,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B292">
         <v>15.51836</v>
@@ -17858,7 +18351,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B293">
         <v>15.641</v>
@@ -17887,7 +18380,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B294">
         <v>10.45379</v>
@@ -17916,7 +18409,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="B295">
         <v>10.43214</v>
@@ -17945,7 +18438,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B296">
         <v>8.70067</v>
@@ -17974,7 +18467,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B297">
         <v>9.61691</v>
@@ -18003,7 +18496,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B298">
         <v>9.08303</v>
@@ -18032,7 +18525,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B299">
         <v>8.82331</v>
@@ -18061,7 +18554,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B300">
         <v>10.48986</v>
@@ -18090,7 +18583,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B301">
         <v>10.36721</v>
@@ -18119,7 +18612,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B302">
         <v>8.49866</v>
@@ -18148,7 +18641,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B303">
         <v>8.99646</v>
@@ -18177,7 +18670,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B304">
         <v>9.11911</v>
@@ -18206,7 +18699,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B305">
         <v>10.40328</v>
@@ -18235,7 +18728,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B306">
         <v>9.90549</v>
@@ -18264,7 +18757,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B307">
         <v>10.12192</v>
@@ -18293,7 +18786,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B308">
         <v>12.71192</v>
@@ -18322,7 +18815,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B309">
         <v>9.82613</v>
@@ -18351,7 +18844,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B310">
         <v>9.84777</v>
@@ -18380,7 +18873,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B311">
         <v>12.3512</v>
@@ -18409,7 +18902,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B312">
         <v>9.39326</v>
@@ -18438,7 +18931,7 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B313">
         <v>9.74677</v>
@@ -18467,7 +18960,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B314">
         <v>12.71192</v>
@@ -18496,7 +18989,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="B315">
         <v>10.98766</v>
@@ -18525,7 +19018,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B316">
         <v>12.09869</v>
@@ -18554,7 +19047,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B317">
         <v>14.11875</v>
@@ -18583,7 +19076,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B318">
         <v>14.47226</v>
@@ -18612,7 +19105,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B319">
         <v>11.31231</v>
@@ -18641,7 +19134,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B320">
         <v>11.44217</v>
@@ -18670,7 +19163,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="B321">
         <v>11.42053</v>
@@ -18699,7 +19192,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B322">
         <v>9.34997</v>
@@ -18728,7 +19221,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B323">
         <v>9.48704</v>
@@ -18757,7 +19250,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B324">
         <v>9.57362</v>
@@ -18786,7 +19279,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B325">
         <v>9.04696</v>
@@ -18815,7 +19308,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B326">
         <v>9.95599</v>
@@ -18844,7 +19337,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B327">
         <v>10.08585</v>
@@ -18873,7 +19366,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B328">
         <v>9.92713</v>
@@ -18902,7 +19395,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B329">
         <v>8.88103</v>
@@ -18931,7 +19424,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B330">
         <v>9.50147</v>
@@ -18960,7 +19453,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B331">
         <v>10.63415</v>
@@ -18989,7 +19482,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B332">
         <v>9.85498</v>
@@ -19018,7 +19511,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B333">
         <v>10.94437</v>
@@ -19047,7 +19540,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B334">
         <v>10.85058</v>
@@ -19076,7 +19569,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B335">
         <v>11.26902</v>
@@ -19105,7 +19598,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B336">
         <v>10.69908</v>
@@ -19134,7 +19627,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B337">
         <v>11.49989</v>
@@ -19163,7 +19656,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B338">
         <v>10.22292</v>
@@ -19192,7 +19685,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B339">
         <v>10.17242</v>
@@ -19221,7 +19714,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B340">
         <v>11.14638</v>
@@ -19250,7 +19743,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B341">
         <v>10.67744</v>
@@ -19279,7 +19772,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B342">
         <v>13.39008</v>
@@ -19308,7 +19801,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B343">
         <v>11.01652</v>
@@ -19337,7 +19830,7 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B344">
         <v>10.33835</v>
@@ -19366,7 +19859,7 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B345">
         <v>11.82454</v>
@@ -19395,7 +19888,7 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B346">
         <v>10.45379</v>
@@ -19424,7 +19917,7 @@
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B347">
         <v>10.32393</v>
@@ -19453,7 +19946,7 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B348">
         <v>14.5949</v>
@@ -19482,7 +19975,7 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B349">
         <v>11.68025</v>
@@ -19511,7 +20004,7 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B350">
         <v>10.07142</v>
@@ -19540,7 +20033,7 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B351">
         <v>9.98484</v>
@@ -19569,7 +20062,7 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B352">
         <v>13.55602</v>
@@ -19598,7 +20091,7 @@
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B353">
         <v>13.88788</v>
@@ -19627,7 +20120,7 @@
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B354">
         <v>10.63415</v>
@@ -19656,7 +20149,7 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B355">
         <v>13.51273</v>
@@ -19685,7 +20178,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B356">
         <v>11.96161</v>
@@ -19714,7 +20207,7 @@
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B357">
         <v>10.39607</v>
@@ -19743,7 +20236,7 @@
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B358">
         <v>9.71791</v>
@@ -19772,7 +20265,7 @@
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B359">
         <v>10.461</v>
@@ -19801,7 +20294,7 @@
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B360">
         <v>15.22978</v>
@@ -19830,7 +20323,7 @@
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B361">
         <v>12.18526</v>
@@ -19859,7 +20352,7 @@
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B362">
         <v>11.25459</v>
@@ -19888,7 +20381,7 @@
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B363">
         <v>11.47103</v>
@@ -19917,7 +20410,7 @@
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B364">
         <v>12.14198</v>
@@ -19946,7 +20439,7 @@
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B365">
         <v>10.8578</v>
@@ -19975,7 +20468,7 @@
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B366">
         <v>10.91551</v>
@@ -20004,7 +20497,7 @@
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B367">
         <v>10.32393</v>
@@ -20033,7 +20526,7 @@
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B368">
         <v>10.36</v>
@@ -20062,7 +20555,7 @@
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B369">
         <v>14.42175</v>
@@ -20091,7 +20584,7 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B370">
         <v>13.06543</v>
@@ -20120,7 +20613,7 @@
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B371">
         <v>14.53719</v>
@@ -20149,7 +20642,7 @@
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B372">
         <v>16.36967</v>
@@ -20178,7 +20671,7 @@
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B373">
         <v>13.18808</v>
@@ -20207,7 +20700,7 @@
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B374">
         <v>11.81732</v>
@@ -20236,7 +20729,7 @@
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B375">
         <v>10.17964</v>
@@ -20265,7 +20758,7 @@
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B376">
         <v>13.27465</v>
@@ -20294,7 +20787,7 @@
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B377">
         <v>10.8578</v>
@@ -20323,7 +20816,7 @@
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B378">
         <v>9.68905</v>
@@ -20352,7 +20845,7 @@
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B379">
         <v>12.48827</v>
@@ -20381,7 +20874,7 @@
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B380">
         <v>10.20849</v>
@@ -20410,7 +20903,7 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B381">
         <v>9.93434</v>
@@ -20439,7 +20932,7 @@
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B382">
         <v>8.79445</v>
@@ -20468,7 +20961,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B383">
         <v>10.9588</v>
@@ -20497,7 +20990,7 @@
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B384">
         <v>10.38164</v>
@@ -20526,7 +21019,7 @@
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B385">
         <v>8.46259</v>
@@ -20555,7 +21048,7 @@
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B386">
         <v>8.45537</v>
@@ -20584,7 +21077,7 @@
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B387">
         <v>9.28504</v>
@@ -20613,7 +21106,7 @@
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B388">
         <v>8.75838</v>
@@ -20642,7 +21135,7 @@
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B389">
         <v>8.98203</v>
@@ -20671,7 +21164,7 @@
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B390">
         <v>9.61691</v>
@@ -20700,7 +21193,7 @@
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B391">
         <v>9.48704</v>
@@ -20729,7 +21222,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B392">
         <v>8.5203</v>
@@ -20758,7 +21251,7 @@
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B393">
         <v>8.19565</v>
@@ -20787,7 +21280,7 @@
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B394">
         <v>10.44657</v>
@@ -20816,7 +21309,7 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B395">
         <v>8.97482</v>
@@ -20845,7 +21338,7 @@
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B396">
         <v>9.03253</v>
@@ -20874,7 +21367,7 @@
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B397">
         <v>9.77562</v>
@@ -20903,7 +21396,7 @@
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B398">
         <v>10.3095</v>
@@ -20932,7 +21425,7 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B399">
         <v>8.9171</v>
@@ -20961,7 +21454,7 @@
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B400">
         <v>8.18844</v>
@@ -20990,7 +21483,7 @@
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B401">
         <v>9.29947</v>
@@ -21019,7 +21512,7 @@
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B402">
         <v>8.62852</v>
@@ -21048,7 +21541,7 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B403">
         <v>9.77562</v>
@@ -21077,7 +21570,7 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B404">
         <v>9.86941</v>
@@ -21106,7 +21599,7 @@
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B405">
         <v>10.11471</v>
@@ -21135,7 +21628,7 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B406">
         <v>9.22732</v>
@@ -21164,7 +21657,7 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B407">
         <v>8.2173</v>
@@ -21193,7 +21686,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B408">
         <v>8.72231</v>
@@ -21222,7 +21715,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B409">
         <v>8.8666</v>
@@ -21251,7 +21744,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B410">
         <v>8.69345</v>
@@ -21280,7 +21773,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B411">
         <v>8.96039</v>
@@ -21309,7 +21802,7 @@
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B412">
         <v>8.66459</v>
@@ -21338,7 +21831,7 @@
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B413">
         <v>8.80167</v>
@@ -21367,7 +21860,7 @@
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B414">
         <v>8.50587</v>
@@ -21396,7 +21889,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B415">
         <v>8.28944</v>
@@ -21425,7 +21918,7 @@
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B416">
         <v>8.23172</v>
@@ -21454,7 +21947,7 @@
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="B417">
         <v>8.47702</v>
@@ -21483,7 +21976,7 @@
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B418">
         <v>9.84777</v>
@@ -21512,7 +22005,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B419">
         <v>10.09306</v>
@@ -21541,7 +22034,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B420">
         <v>9.3139</v>
@@ -21570,7 +22063,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B421">
         <v>8.67902</v>
@@ -21599,7 +22092,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B422">
         <v>10.04256</v>
@@ -21628,7 +22121,7 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="B423">
         <v>9.69627</v>
@@ -21657,7 +22150,7 @@
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B424">
         <v>10.13635</v>
@@ -21686,7 +22179,7 @@
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B425">
         <v>8.75838</v>
@@ -21715,7 +22208,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B426">
         <v>9.08303</v>
@@ -21744,7 +22237,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B427">
         <v>8.25337</v>
@@ -21773,7 +22266,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B428">
         <v>7.81328</v>
@@ -21802,7 +22295,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B429">
         <v>8.14515</v>
@@ -21831,7 +22324,7 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B430">
         <v>7.81328</v>
@@ -21860,7 +22353,7 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B431">
         <v>7.49585</v>
@@ -21889,7 +22382,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B432">
         <v>8.71509</v>
@@ -21918,7 +22411,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="B433">
         <v>9.29225</v>
@@ -21947,7 +22440,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B434">
         <v>7.95757</v>
@@ -21976,7 +22469,7 @@
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B435">
         <v>7.87821</v>
@@ -22005,7 +22498,7 @@
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B436">
         <v>7.91429</v>
@@ -22034,7 +22527,7 @@
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B437">
         <v>8.49145</v>
@@ -22063,7 +22556,7 @@
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="B438">
         <v>9.15518</v>
@@ -22092,7 +22585,7 @@
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B439">
         <v>9.45097</v>
@@ -22121,7 +22614,7 @@
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B440">
         <v>12.49549</v>
@@ -22150,7 +22643,7 @@
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B441">
         <v>9.0181</v>
@@ -22179,7 +22672,7 @@
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B442">
         <v>7.972</v>
@@ -22208,7 +22701,7 @@
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B443">
         <v>10.0137</v>
@@ -22237,7 +22730,7 @@
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B444">
         <v>8.29665</v>
@@ -22266,7 +22759,7 @@
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B445">
         <v>8.55638</v>
@@ -22295,7 +22788,7 @@
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B446">
         <v>9.24175</v>
@@ -22324,7 +22817,7 @@
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B447">
         <v>9.21289</v>
@@ -22353,7 +22846,7 @@
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="B448">
         <v>8.34716</v>
@@ -22382,7 +22875,7 @@
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B449">
         <v>8.68624</v>
@@ -22411,7 +22904,7 @@
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B450">
         <v>10.67022</v>
@@ -22440,7 +22933,7 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="B451">
         <v>8.33273</v>
@@ -22469,7 +22962,7 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="B452">
         <v>8.10186</v>
@@ -22498,7 +22991,7 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B453">
         <v>8.32551</v>
@@ -22527,7 +23020,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="B454">
         <v>8.59245</v>
@@ -22556,7 +23049,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="B455">
         <v>8.9676</v>
@@ -22585,7 +23078,7 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B456">
         <v>9.29225</v>
@@ -22614,7 +23107,7 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="B457">
         <v>10.30228</v>
@@ -22643,7 +23136,7 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B458">
         <v>9.66019</v>
@@ -22672,7 +23165,7 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="B459">
         <v>10.35278</v>
@@ -22701,7 +23194,7 @@
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="B460">
         <v>9.90549</v>
@@ -22730,7 +23223,7 @@
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="B461">
         <v>9.16239</v>
@@ -22759,7 +23252,7 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="B462">
         <v>8.64295</v>
@@ -22788,7 +23281,7 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="B463">
         <v>8.15958</v>
@@ -22817,7 +23310,7 @@
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="B464">
         <v>7.78443</v>
@@ -22846,7 +23339,7 @@
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="B465">
         <v>8.47702</v>
@@ -22875,7 +23368,7 @@
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="B466">
         <v>8.36159</v>
@@ -22904,7 +23397,7 @@
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="B467">
         <v>8.77281</v>
@@ -22933,7 +23426,7 @@
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="B468">
         <v>9.14796</v>
@@ -22962,7 +23455,7 @@
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="B469">
         <v>8.61409</v>
@@ -22991,7 +23484,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="B470">
         <v>8.21008</v>
@@ -23020,7 +23513,7 @@
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="B471">
         <v>7.91429</v>
@@ -23049,7 +23542,7 @@
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="B472">
         <v>7.9215</v>
@@ -23078,7 +23571,7 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B473">
         <v>9.82613</v>
@@ -23107,7 +23600,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B474">
         <v>9.10468</v>
@@ -23136,7 +23629,7 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B475">
         <v>9.3139</v>
@@ -23165,7 +23658,7 @@
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B476">
         <v>9.01089</v>
@@ -23194,7 +23687,7 @@
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B477">
         <v>7.88543</v>
@@ -23223,7 +23716,7 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="B478">
         <v>7.77</v>
@@ -23252,7 +23745,7 @@
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="B479">
         <v>8.24615</v>
@@ -23281,7 +23774,7 @@
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="B480">
         <v>8.00808</v>
@@ -23310,7 +23803,7 @@
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B481">
         <v>9.68905</v>
@@ -23339,7 +23832,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="B482">
         <v>9.0686</v>
@@ -23368,7 +23861,7 @@
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="B483">
         <v>8.30387</v>
@@ -23397,7 +23890,7 @@
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="B484">
         <v>8.13794</v>
@@ -23426,7 +23919,7 @@
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="B485">
         <v>8.4193</v>
@@ -23455,7 +23948,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="B486">
         <v>8.88824</v>
@@ -23484,7 +23977,7 @@
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="B487">
         <v>8.32551</v>
@@ -23513,7 +24006,7 @@
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="B488">
         <v>8.41209</v>
@@ -23542,7 +24035,7 @@
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B489">
         <v>8.60688</v>
@@ -23571,7 +24064,7 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="B490">
         <v>8.85217</v>
@@ -23600,7 +24093,7 @@
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="B491">
         <v>8.65738</v>
@@ -23629,7 +24122,7 @@
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="B492">
         <v>8.29665</v>
@@ -23658,7 +24151,7 @@
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="B493">
         <v>8.95317</v>
@@ -23687,7 +24180,7 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="B494">
         <v>9.03975</v>
@@ -23716,7 +24209,7 @@
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="B495">
         <v>8.4698</v>
@@ -23745,7 +24238,7 @@
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="B496">
         <v>9.40769</v>
@@ -23774,7 +24267,7 @@
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="B497">
         <v>9.65298</v>
@@ -23803,7 +24296,7 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="B498">
         <v>9.30668</v>
@@ -23832,7 +24325,7 @@
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="B499">
         <v>10.87944</v>
@@ -23861,7 +24354,7 @@
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="B500">
         <v>9.19847</v>
@@ -23890,7 +24383,7 @@
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B501">
         <v>9.34997</v>
@@ -23919,7 +24412,7 @@
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="B502">
         <v>8.50587</v>
@@ -23948,7 +24441,7 @@
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="B503">
         <v>9.42211</v>
@@ -23977,7 +24470,7 @@
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="B504">
         <v>10.29507</v>
@@ -24006,7 +24499,7 @@
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="B505">
         <v>11.58646</v>
@@ -24035,7 +24528,7 @@
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="B506">
         <v>11.12473</v>
@@ -24064,7 +24557,7 @@
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="B507">
         <v>9.11911</v>
@@ -24093,7 +24586,7 @@
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="B508">
         <v>7.972</v>
@@ -24122,7 +24615,7 @@
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="B509">
         <v>8.06579</v>
@@ -24151,7 +24644,7 @@
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B510">
         <v>8.08022</v>
@@ -24180,7 +24673,7 @@
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="B511">
         <v>7.79886</v>
@@ -24209,7 +24702,7 @@
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="B512">
         <v>7.40927</v>
@@ -24238,7 +24731,7 @@
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="B513">
         <v>10.28064</v>
@@ -24267,7 +24760,7 @@
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="B514">
         <v>7.51028</v>
@@ -24296,7 +24789,7 @@
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="B515">
         <v>7.91429</v>
@@ -24325,7 +24818,7 @@
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="B516">
         <v>8.57081</v>
@@ -24354,7 +24847,7 @@
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="B517">
         <v>8.67902</v>
@@ -24383,7 +24876,7 @@
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="B518">
         <v>9.71791</v>
@@ -24412,7 +24905,7 @@
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="B519">
         <v>12.96443</v>
@@ -24441,7 +24934,7 @@
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="B520">
         <v>7.84214</v>
@@ -24470,7 +24963,7 @@
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B521">
         <v>7.11348</v>
@@ -24499,7 +24992,7 @@
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B522">
         <v>9.55198</v>
@@ -24528,7 +25021,7 @@
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="B523">
         <v>8.31108</v>
@@ -24557,7 +25050,7 @@
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B524">
         <v>8.85938</v>
@@ -24586,7 +25079,7 @@
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="B525">
         <v>8.39044</v>
@@ -24615,7 +25108,7 @@
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="B526">
         <v>7.23613</v>
@@ -24644,7 +25137,7 @@
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="B527">
         <v>7.58242</v>
@@ -24673,7 +25166,7 @@
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="B528">
         <v>8.3688</v>
@@ -24702,7 +25195,7 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="B529">
         <v>8.33273</v>
@@ -24731,7 +25224,7 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="B530">
         <v>8.78724</v>
@@ -24760,7 +25253,7 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="B531">
         <v>8.80888</v>
@@ -24789,7 +25282,7 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="B532">
         <v>8.43373</v>
@@ -24818,7 +25311,7 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="B533">
         <v>7.51028</v>
@@ -24847,7 +25340,7 @@
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="B534">
         <v>7.63292</v>
@@ -24876,7 +25369,7 @@
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="B535">
         <v>11.08866</v>
@@ -24905,7 +25398,7 @@
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="B536">
         <v>7.77721</v>
@@ -24934,7 +25427,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="B537">
         <v>7.96479</v>
@@ -24963,7 +25456,7 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="B538">
         <v>7.60406</v>
@@ -24992,7 +25485,7 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="B539">
         <v>7.65457</v>
@@ -25021,7 +25514,7 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="B540">
         <v>7.10626</v>
@@ -25050,7 +25543,7 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="B541">
         <v>8.21008</v>
@@ -25079,7 +25572,7 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="B542">
         <v>8.24615</v>
@@ -25108,7 +25601,7 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="B543">
         <v>7.77</v>
@@ -25137,7 +25630,7 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="B544">
         <v>7.69785</v>
@@ -25166,7 +25659,7 @@
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="B545">
         <v>9.33554</v>
@@ -25195,7 +25688,7 @@
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="B546">
         <v>8.62852</v>
@@ -25224,7 +25717,7 @@
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="B547">
         <v>11.99769</v>
@@ -25253,7 +25746,7 @@
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="B548">
         <v>9.37883</v>
@@ -25282,7 +25775,7 @@
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="B549">
         <v>8.9171</v>
@@ -25311,7 +25804,7 @@
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="B550">
         <v>8.09465</v>
@@ -25340,7 +25833,7 @@
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="B551">
         <v>8.96039</v>
@@ -25369,7 +25862,7 @@
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="B552">
         <v>9.52312</v>
@@ -25398,7 +25891,7 @@
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="B553">
         <v>8.92432</v>
@@ -25427,7 +25920,7 @@
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="B554">
         <v>9.22011</v>
@@ -25456,7 +25949,7 @@
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B555">
         <v>7.26498</v>
@@ -25485,7 +25978,7 @@
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B556">
         <v>7.53913</v>
@@ -25514,7 +26007,7 @@
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="B557">
         <v>17.87749</v>
@@ -25543,7 +26036,7 @@
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="B558">
         <v>10.23014</v>
@@ -25572,7 +26065,7 @@
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="B559">
         <v>9.55198</v>
@@ -25601,7 +26094,7 @@
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="B560">
         <v>9.28504</v>
@@ -25630,7 +26123,7 @@
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="B561">
         <v>7.24334</v>
@@ -25659,7 +26152,7 @@
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="B562">
         <v>7.77</v>
@@ -25688,7 +26181,7 @@
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B563">
         <v>8.79445</v>
@@ -25717,7 +26210,7 @@
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="B564">
         <v>9.66019</v>
@@ -25746,7 +26239,7 @@
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="B565">
         <v>12.18526</v>
@@ -25775,7 +26268,7 @@
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="B566">
         <v>9.28504</v>
@@ -25804,7 +26297,7 @@
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="B567">
         <v>8.24615</v>
@@ -25833,7 +26326,7 @@
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="B568">
         <v>9.63133</v>
@@ -25862,7 +26355,7 @@
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="B569">
         <v>7.84214</v>
@@ -25891,7 +26384,7 @@
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="B570">
         <v>9.23454</v>
@@ -25920,7 +26413,7 @@
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="B571">
         <v>8.15236</v>
@@ -25949,7 +26442,7 @@
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="B572">
         <v>7.64014</v>
@@ -25978,7 +26471,7 @@
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="B573">
         <v>8.74395</v>
@@ -26007,7 +26500,7 @@
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="B574">
         <v>8.58523</v>
@@ -26036,7 +26529,7 @@
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="B575">
         <v>10.43936</v>
@@ -26065,7 +26558,7 @@
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="B576">
         <v>7.4237</v>
@@ -26094,7 +26587,7 @@
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="B577">
         <v>7.871</v>
@@ -26123,7 +26616,7 @@
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="B578">
         <v>7.79164</v>
@@ -26152,7 +26645,7 @@
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="B579">
         <v>8.69345</v>
@@ -26181,7 +26674,7 @@
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="B580">
         <v>8.80888</v>
@@ -26210,7 +26703,7 @@
     </row>
     <row r="581" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="B581">
         <v>11.69468</v>
@@ -26239,7 +26732,7 @@
     </row>
     <row r="582" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="B582">
         <v>8.17401</v>
@@ -26268,7 +26761,7 @@
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="B583">
         <v>7.48142</v>
@@ -26297,7 +26790,7 @@
     </row>
     <row r="584" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="B584">
         <v>7.40927</v>
@@ -26326,7 +26819,7 @@
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="B585">
         <v>9.58083</v>
@@ -26355,7 +26848,7 @@
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="B586">
         <v>8.72952</v>
@@ -26384,7 +26877,7 @@
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="B587">
         <v>7.80607</v>
@@ -26413,7 +26906,7 @@
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="B588">
         <v>8.33273</v>
@@ -26442,7 +26935,7 @@
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B589">
         <v>9.64576</v>
@@ -26471,7 +26964,7 @@
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="B590">
         <v>8.88824</v>
@@ -26500,7 +26993,7 @@
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="B591">
         <v>7.11348</v>
@@ -26529,7 +27022,7 @@
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="B592">
         <v>7.94314</v>
@@ -26558,7 +27051,7 @@
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B593">
         <v>9.37161</v>
@@ -26587,7 +27080,7 @@
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="B594">
         <v>8.88824</v>
@@ -26616,7 +27109,7 @@
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="B595">
         <v>7.30106</v>
@@ -26645,7 +27138,7 @@
     </row>
     <row r="596" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="B596">
         <v>7.07019</v>
@@ -26674,7 +27167,7 @@
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="B597">
         <v>7.09905</v>
@@ -26703,7 +27196,7 @@
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B598">
         <v>21.45588</v>
@@ -26732,7 +27225,7 @@
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="B599">
         <v>10.82173</v>
@@ -26761,7 +27254,7 @@
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="B600">
         <v>8.27501</v>
@@ -26790,7 +27283,7 @@
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="B601">
         <v>8.8666</v>
@@ -26819,7 +27312,7 @@
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="B602">
         <v>7.87821</v>
@@ -26848,7 +27341,7 @@
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="B603">
         <v>6.68061</v>
@@ -26877,7 +27370,7 @@
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="B604">
         <v>9.68184</v>
@@ -26906,7 +27399,7 @@
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="B605">
         <v>8.79445</v>
@@ -26935,7 +27428,7 @@
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="B606">
         <v>6.91147</v>
@@ -26964,7 +27457,7 @@
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B607">
         <v>7.96479</v>
@@ -26993,7 +27486,7 @@
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="B608">
         <v>7.51028</v>
@@ -27022,7 +27515,7 @@
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="B609">
         <v>6.38482</v>
@@ -27051,7 +27544,7 @@
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="B610">
         <v>6.18281</v>
@@ -27080,7 +27573,7 @@
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="B611">
         <v>8.78724</v>
@@ -27109,7 +27602,7 @@
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="B612">
         <v>6.55796</v>
@@ -27138,7 +27631,7 @@
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="B613">
         <v>8.14515</v>
@@ -27167,7 +27660,7 @@
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="B614">
         <v>6.8754</v>
@@ -27196,7 +27689,7 @@
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="B615">
         <v>8.61409</v>
@@ -27225,7 +27718,7 @@
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="B616">
         <v>8.08022</v>
@@ -27254,7 +27747,7 @@
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="B617">
         <v>6.38482</v>
@@ -27283,7 +27776,7 @@
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="B618">
         <v>6.03131</v>
@@ -27312,7 +27805,7 @@
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="B619">
         <v>6.49303</v>
@@ -27341,7 +27834,7 @@
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="B620">
         <v>6.71668</v>
@@ -27370,7 +27863,7 @@
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="B621">
         <v>6.29824</v>
@@ -27399,7 +27892,7 @@
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="B622">
         <v>6.44253</v>
@@ -27428,7 +27921,7 @@
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="B623">
         <v>6.55796</v>
@@ -27457,7 +27950,7 @@
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="B624">
         <v>6.52189</v>
@@ -27486,7 +27979,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B625">
         <v>7.10626</v>
@@ -27515,7 +28008,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="B626">
         <v>7.38763</v>
@@ -27544,7 +28037,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="B627">
         <v>7.40927</v>
@@ -27573,7 +28066,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="B628">
         <v>11.20409</v>
@@ -27602,7 +28095,7 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="B629">
         <v>11.44217</v>
@@ -27631,7 +28124,7 @@
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="B630">
         <v>6.68061</v>
@@ -27660,7 +28153,7 @@
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="B631">
         <v>7.56799</v>
@@ -27689,7 +28182,7 @@
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="B632">
         <v>6.83933</v>
@@ -27718,7 +28211,7 @@
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="B633">
         <v>6.83933</v>
@@ -27747,7 +28240,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="B634">
         <v>6.78161</v>
@@ -27776,7 +28269,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="B635">
         <v>6.76718</v>
@@ -27805,7 +28298,7 @@
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="B636">
         <v>6.60125</v>
@@ -27834,7 +28327,7 @@
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="B637">
         <v>5.62729</v>
@@ -27863,7 +28356,7 @@
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="B638">
         <v>6.11788</v>
@@ -27892,7 +28385,7 @@
     </row>
     <row r="639" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="B639">
         <v>6.03852</v>
@@ -27921,7 +28414,7 @@
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="B640">
         <v>8.59966</v>
@@ -27950,7 +28443,7 @@
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="B641">
         <v>7.25777</v>
@@ -27979,7 +28472,7 @@
     </row>
     <row r="642" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="B642">
         <v>7.56799</v>
@@ -28008,7 +28501,7 @@
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="B643">
         <v>7.20727</v>
@@ -28037,7 +28530,7 @@
     </row>
     <row r="644" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="B644">
         <v>8.44816</v>
@@ -28066,7 +28559,7 @@
     </row>
     <row r="645" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="B645">
         <v>8.01529</v>
@@ -28095,7 +28588,7 @@
     </row>
     <row r="646" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B646">
         <v>7.35156</v>
@@ -28124,7 +28617,7 @@
     </row>
     <row r="647" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="B647">
         <v>9.02532</v>
@@ -28153,7 +28646,7 @@
     </row>
     <row r="648" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="B648">
         <v>9.97763</v>
@@ -28182,7 +28675,7 @@
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="B649">
         <v>8.00086</v>
@@ -28211,7 +28704,7 @@
     </row>
     <row r="650" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="B650">
         <v>7.12069</v>
@@ -28240,7 +28733,7 @@
     </row>
     <row r="651" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="B651">
         <v>6.09624</v>
@@ -28269,7 +28762,7 @@
     </row>
     <row r="652" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="B652">
         <v>6.16117</v>
@@ -28298,7 +28791,7 @@
     </row>
     <row r="653" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="B653">
         <v>8.93153</v>
@@ -28327,7 +28820,7 @@
     </row>
     <row r="654" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="B654">
         <v>7.10626</v>
@@ -28356,7 +28849,7 @@
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="B655">
         <v>6.85376</v>
@@ -28385,7 +28878,7 @@
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="B656">
         <v>8.72952</v>
@@ -28414,7 +28907,7 @@
     </row>
     <row r="657" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="B657">
         <v>8.57802</v>
@@ -28443,7 +28936,7 @@
     </row>
     <row r="658" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="B658">
         <v>7.24334</v>
@@ -28472,7 +28965,7 @@
     </row>
     <row r="659" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="B659">
         <v>7.73392</v>
@@ -28501,7 +28994,7 @@
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="B660">
         <v>8.71509</v>
@@ -28530,7 +29023,7 @@
     </row>
     <row r="661" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="B661">
         <v>7.74835</v>
@@ -28559,7 +29052,7 @@
     </row>
     <row r="662" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B662">
         <v>7.69785</v>
@@ -28588,7 +29081,7 @@
     </row>
     <row r="663" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="B663">
         <v>7.34434</v>
@@ -28617,7 +29110,7 @@
     </row>
     <row r="664" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="B664">
         <v>6.83933</v>
@@ -28646,7 +29139,7 @@
     </row>
     <row r="665" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="B665">
         <v>6.26938</v>
@@ -28675,7 +29168,7 @@
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="B666">
         <v>6.4281</v>
@@ -28704,7 +29197,7 @@
     </row>
     <row r="667" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B667">
         <v>6.42089</v>
@@ -28733,7 +29226,7 @@
     </row>
     <row r="668" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B668">
         <v>6.48582</v>
@@ -28762,7 +29255,7 @@
     </row>
     <row r="669" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="B669">
         <v>7.07741</v>
@@ -28791,7 +29284,7 @@
     </row>
     <row r="670" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="B670">
         <v>6.73111</v>
@@ -28820,7 +29313,7 @@
     </row>
     <row r="671" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="B671">
         <v>6.96197</v>
@@ -28849,7 +29342,7 @@
     </row>
     <row r="672" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="B672">
         <v>6.16117</v>
@@ -28878,7 +29371,7 @@
     </row>
     <row r="673" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="B673">
         <v>6.40646</v>
@@ -28907,7 +29400,7 @@
     </row>
     <row r="674" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="B674">
         <v>6.19002</v>
@@ -28936,7 +29429,7 @@
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="B675">
         <v>6.4281</v>
@@ -28965,7 +29458,7 @@
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B676">
         <v>8.41209</v>
@@ -28994,7 +29487,7 @@
     </row>
     <row r="677" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="B677">
         <v>9.5159</v>
@@ -29023,7 +29516,7 @@
     </row>
     <row r="678" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="B678">
         <v>8.85217</v>
@@ -29052,7 +29545,7 @@
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="B679">
         <v>7.49585</v>
@@ -29081,7 +29574,7 @@
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="B680">
         <v>6.86819</v>
@@ -29110,7 +29603,7 @@
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="B681">
         <v>7.97922</v>
@@ -29139,7 +29632,7 @@
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="B682">
         <v>7.43813</v>
@@ -29168,7 +29661,7 @@
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="B683">
         <v>7.13512</v>
@@ -29197,7 +29690,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="B684">
         <v>7.30827</v>
@@ -29226,7 +29719,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="B685">
         <v>8.89546</v>
@@ -29255,7 +29748,7 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>794</v>
+        <v>805</v>
       </c>
       <c r="B686">
         <v>10.92994</v>
@@ -29284,7 +29777,7 @@
     </row>
     <row r="687" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="B687">
         <v>8.30387</v>
@@ -29313,7 +29806,7 @@
     </row>
     <row r="688" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="B688">
         <v>6.46418</v>
@@ -29342,7 +29835,7 @@
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="B689">
         <v>6.6734</v>
@@ -29371,7 +29864,7 @@
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="B690">
         <v>7.25777</v>
@@ -29400,7 +29893,7 @@
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="B691">
         <v>8.62131</v>
@@ -29429,7 +29922,7 @@
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="B692">
         <v>9.7612</v>
@@ -29458,7 +29951,7 @@
     </row>
     <row r="693" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="B693">
         <v>6.7239</v>
@@ -29487,7 +29980,7 @@
     </row>
     <row r="694" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="B694">
         <v>6.43532</v>
@@ -29516,7 +30009,7 @@
     </row>
     <row r="695" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="B695">
         <v>7.21448</v>
@@ -29545,7 +30038,7 @@
     </row>
     <row r="696" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="B696">
         <v>7.56799</v>
@@ -29574,7 +30067,7 @@
     </row>
     <row r="697" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="B697">
         <v>8.54195</v>
@@ -29603,7 +30096,7 @@
     </row>
     <row r="698" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="B698">
         <v>10.78565</v>
@@ -29632,7 +30125,7 @@
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="B699">
         <v>8.4698</v>
@@ -29661,7 +30154,7 @@
     </row>
     <row r="700" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B700">
         <v>8.06579</v>
@@ -29690,7 +30183,7 @@
     </row>
     <row r="701" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="B701">
         <v>10.15799</v>
@@ -29719,7 +30212,7 @@
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="B702">
         <v>8.89546</v>
@@ -29748,7 +30241,7 @@
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="B703">
         <v>7.24334</v>
@@ -29777,7 +30270,7 @@
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="B704">
         <v>6.84654</v>
@@ -29806,7 +30299,7 @@
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="B705">
         <v>7.62571</v>
@@ -29835,7 +30328,7 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="B706">
         <v>6.98362</v>
@@ -29864,7 +30357,7 @@
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B707">
         <v>6.99083</v>
@@ -29893,7 +30386,7 @@
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="B708">
         <v>6.98362</v>
@@ -29922,7 +30415,7 @@
     </row>
     <row r="709" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="B709">
         <v>6.44253</v>
@@ -29951,7 +30444,7 @@
     </row>
     <row r="710" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="B710">
         <v>7.58242</v>
@@ -29980,7 +30473,7 @@
     </row>
     <row r="711" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="B711">
         <v>6.74554</v>
@@ -30009,7 +30502,7 @@
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
       <c r="B712">
         <v>8.05136</v>
@@ -30038,7 +30531,7 @@
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="B713">
         <v>8.20287</v>
@@ -30067,7 +30560,7 @@
     </row>
     <row r="714" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="B714">
         <v>7.68342</v>
@@ -30096,7 +30589,7 @@
     </row>
     <row r="715" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="B715">
         <v>7.53192</v>
@@ -30125,7 +30618,7 @@
     </row>
     <row r="716" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="B716">
         <v>8.28223</v>
@@ -30154,7 +30647,7 @@
     </row>
     <row r="717" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="B717">
         <v>7.64014</v>
@@ -30183,7 +30676,7 @@
     </row>
     <row r="718" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="B718">
         <v>8.46259</v>
@@ -30212,7 +30705,7 @@
     </row>
     <row r="719" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="B719">
         <v>8.24615</v>
@@ -30241,7 +30734,7 @@
     </row>
     <row r="720" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="B720">
         <v>8.14515</v>
@@ -30270,7 +30763,7 @@
     </row>
     <row r="721" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="B721">
         <v>7.63292</v>
@@ -30299,7 +30792,7 @@
     </row>
     <row r="722" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="B722">
         <v>8.4698</v>
@@ -30328,7 +30821,7 @@
     </row>
     <row r="723" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="B723">
         <v>8.39766</v>
@@ -30357,7 +30850,7 @@
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="B724">
         <v>7.18562</v>
@@ -30386,7 +30879,7 @@
     </row>
     <row r="725" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="B725">
         <v>8.85938</v>
@@ -30415,7 +30908,7 @@
     </row>
     <row r="726" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="B726">
         <v>10.38164</v>
@@ -30444,7 +30937,7 @@
     </row>
     <row r="727" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="B727">
         <v>8.17401</v>
@@ -30473,7 +30966,7 @@
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="B728">
         <v>6.31989</v>
@@ -30502,7 +30995,7 @@
     </row>
     <row r="729" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="B729">
         <v>6.55075</v>
@@ -30531,7 +31024,7 @@
     </row>
     <row r="730" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="B730">
         <v>6.11067</v>
@@ -30560,7 +31053,7 @@
     </row>
     <row r="731" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="B731">
         <v>5.69222</v>
